--- a/detector_fugas_v1.xlsx
+++ b/detector_fugas_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://financialmerc-my.sharepoint.com/personal/j_eduardo_bucio_financialmerc_com/Documents/0. Ventas Digitales Claude/Automatizaciones N8n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_0D7823C610818E53C6A23C1FA0ACA06AE9CC9329" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C402EAE7-A568-4CF8-A6ED-8E77046C9BBF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08DA680E-E6C7-4C21-8532-00A3CB74D9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🏠 Inicio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="📊 Resumen Mensual" sheetId="5" r:id="rId5"/>
     <sheet name="🎯 Plan de Rescate" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
   <si>
     <t>💸  DETECTOR DE FUGAS — Control de Gastos Hormiga</t>
   </si>
@@ -67,7 +67,9 @@
   </si>
   <si>
     <t>Hoja 🔍 Detector Hormiga
-Ve exactamente qué categorías se están comiendo tu dinero</t>
+Ve exactamente qué categorías se están comiendo tu dinero
+Hoja 🎯 Plan de Rescate
+Calcula cuánto recuperas eliminando cada categoría</t>
   </si>
   <si>
     <t>📂  HOJAS DE ESTE SISTEMA</t>
@@ -100,7 +102,7 @@
     <t>🎯 Plan de Rescate</t>
   </si>
   <si>
-    <t>Calcula cuánto te ahorrará eliminar cada categoría hormiga</t>
+    <t>Calcula cuánto recuperas al reducir cada gasto hormiga</t>
   </si>
   <si>
     <t>🔒  Tus datos no salen de este archivo. No hay conexión a internet, no hay suscripción. Es tuyo.</t>
@@ -463,10 +465,7 @@
     <t>¿Vale la pena?</t>
   </si>
   <si>
-    <t>Compromiso</t>
-  </si>
-  <si>
-    <t>Escribe aquí tu compromiso</t>
+    <t>✏️ Mi compromiso (escribe aquí)</t>
   </si>
   <si>
     <t>🏆  TOTAL RECUPERABLE</t>
@@ -1221,7 +1220,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="3" customWidth="1"/>
@@ -1456,7 +1455,7 @@
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
         <v>30</v>
       </c>
@@ -2494,6 +2493,21 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Categoría no válida" error="Usa una de las categorías del menú para que el Detector funcione correctamente." promptTitle="Categoría" prompt="Elige una categoría de la lista" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>'⚙️ Config'!$C$13:$C$22</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>C4:C63</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2602,7 +2616,7 @@
       <c r="F14" s="75"/>
       <c r="G14" s="75"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>112</v>
       </c>
@@ -3017,7 +3031,7 @@
       <c r="E13" s="75"/>
       <c r="F13" s="75"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>112</v>
       </c>
@@ -3283,7 +3297,7 @@
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -3306,7 +3320,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="58" t="s">
         <v>112</v>
       </c>
@@ -3352,9 +3366,7 @@
         <f t="shared" ref="G6:G15" si="2">IF(E6=0,"Sin gasto","⬇️ Reducir "&amp;TEXT(D6,"0%")&amp;" = "&amp;TEXT(E6,"$#,##0")&amp;"/mes")</f>
         <v>⬇️ Reducir 20% = $30/mes</v>
       </c>
-      <c r="H6" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
@@ -3379,9 +3391,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $89/mes</v>
       </c>
-      <c r="H7" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="53" t="s">
@@ -3406,9 +3416,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $16/mes</v>
       </c>
-      <c r="H8" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H8" s="63"/>
     </row>
     <row r="9" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
@@ -3433,9 +3441,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $111/mes</v>
       </c>
-      <c r="H9" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H9" s="63"/>
     </row>
     <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="53" t="s">
@@ -3460,9 +3466,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $8/mes</v>
       </c>
-      <c r="H10" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="54" t="s">
@@ -3487,9 +3491,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $13/mes</v>
       </c>
-      <c r="H11" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H11" s="63"/>
     </row>
     <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="53" t="s">
@@ -3514,9 +3516,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $38/mes</v>
       </c>
-      <c r="H12" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H12" s="63"/>
     </row>
     <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="54" t="s">
@@ -3541,9 +3541,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $29/mes</v>
       </c>
-      <c r="H13" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H13" s="63"/>
     </row>
     <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53" t="s">
@@ -3568,9 +3566,7 @@
         <f t="shared" si="2"/>
         <v>⬇️ Reducir 20% = $10/mes</v>
       </c>
-      <c r="H14" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H14" s="63"/>
     </row>
     <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="54" t="s">
@@ -3595,13 +3591,11 @@
         <f t="shared" si="2"/>
         <v>Sin gasto</v>
       </c>
-      <c r="H15" s="63" t="s">
-        <v>140</v>
-      </c>
+      <c r="H15" s="63"/>
     </row>
     <row r="16" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" s="68">
         <f>SUM(C6:C15)</f>
